--- a/sheets/대금율보/검수/달도밝은데.xlsx
+++ b/sheets/대금율보/검수/달도밝은데.xlsx
@@ -5644,7 +5644,7 @@
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△無‹</t>
+△無</t>
         </is>
       </c>
       <c r="I9" s="25" t="inlineStr">
@@ -5670,7 +5670,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰浹</t>
         </is>
       </c>
@@ -5734,7 +5734,7 @@
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南‹
+          <t xml:space="preserve">–南
 –無</t>
         </is>
       </c>
@@ -5761,7 +5761,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潕湳</t>
         </is>
       </c>
@@ -5822,7 +5822,7 @@
       <c r="C13" s="25"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋淋‹
+          <t xml:space="preserve">淋淋
 –汰</t>
         </is>
       </c>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 無汰</t>
         </is>
       </c>
@@ -5933,7 +5933,7 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋淋‹
+          <t xml:space="preserve">淋淋
 –汰</t>
         </is>
       </c>
@@ -6025,14 +6025,14 @@
       <c r="C17" s="25"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰汰‹
+          <t xml:space="preserve">汰汰
 –無</t>
         </is>
       </c>
       <c r="E17" s="25"/>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳潕‹
+          <t xml:space="preserve">湳潕
 –湳</t>
         </is>
       </c>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△無‹
+          <t xml:space="preserve">△無
 –汰</t>
         </is>
       </c>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無汰‹
+          <t xml:space="preserve">無汰
 –汰</t>
         </is>
       </c>
@@ -6169,7 +6169,7 @@
       <c r="C20" s="25"/>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E20" s="25"/>
@@ -6295,7 +6295,7 @@
       <c r="G23" s="22"/>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –汰</t>
         </is>
       </c>
@@ -6306,8 +6306,8 @@
       </c>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
-–汰‹</t>
+          <t xml:space="preserve">林
+–汰</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">浹淋‹
+          <t xml:space="preserve">浹淋
 –淋</t>
         </is>
       </c>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△汰‹
+          <t xml:space="preserve">△汰
 –淋</t>
         </is>
       </c>
@@ -6397,7 +6397,7 @@
       <c r="H25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△浹‹</t>
+△浹</t>
         </is>
       </c>
       <c r="I25" s="25" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="J25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△林‹
+          <t xml:space="preserve">△林
 –無</t>
         </is>
       </c>
@@ -6443,7 +6443,7 @@
       <c r="H26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–浹
-汰浹‹</t>
+汰浹</t>
         </is>
       </c>
       <c r="I26" s="26" t="inlineStr">

--- a/sheets/대금율보/검수/달도밝은데.xlsx
+++ b/sheets/대금율보/검수/달도밝은데.xlsx
@@ -5258,24 +5258,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="121.21" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="90.45" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="90.45" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="25"/>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="90.45" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="M5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="90.45" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="M6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="90.45" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="90.45" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="M8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="90.45" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="M9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="90.45" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="M10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="90.45" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="90.45" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="90.45" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="90.45" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="M14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="90.45" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="90.45" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="90.45" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="M17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="90.45" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M18" s="26"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="90.45" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="90.45" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="25"/>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="M20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="90.45" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="M21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="90.45" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="26"/>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="M22" s="26"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="90.45" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="M23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="90.45" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="25"/>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="M24" s="25"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="90.45" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="25"/>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="M25" s="25"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="90.45" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="26"/>
@@ -6476,6 +6476,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="33"/>
 </worksheet>
 </file>